--- a/2026/BRIN 3219/Abril/BRIN3219-EXPENSAS-Abril.xlsx
+++ b/2026/BRIN 3219/Abril/BRIN3219-EXPENSAS-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8103A8A-2337-4ECE-8E58-68EFBAE8C778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21A10E8-3001-4FF9-BDCC-C879015E2358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -26,12 +26,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="159">
   <si>
     <t>U.F.</t>
   </si>
@@ -444,9 +447,6 @@
     <t>7-GASTOS LEGALES</t>
   </si>
   <si>
-    <t>Gabriela</t>
-  </si>
-  <si>
     <t>INTERES por MORA 3,7%</t>
   </si>
   <si>
@@ -492,24 +492,6 @@
     <t>Extraordinarias</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>Sr. Abogado - Escrito para volver a solicitar la activacion de la cuenta bancaria</t>
-  </si>
-  <si>
-    <t>VTO: 17/04</t>
-  </si>
-  <si>
-    <t>MARZO</t>
-  </si>
-  <si>
-    <t>Damato fumigaciones - MARZO</t>
-  </si>
-  <si>
-    <t>Egresos por gastos mes - MARZO</t>
-  </si>
-  <si>
     <t>subidos en m4rz0</t>
   </si>
   <si>
@@ -517,6 +499,30 @@
   </si>
   <si>
     <t>Seguro - Reemplazo</t>
+  </si>
+  <si>
+    <t>VTO: 15/05</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>Damato fumigaciones - ABRIL</t>
+  </si>
+  <si>
+    <t>Egresos por gastos mes - ABRIL</t>
+  </si>
+  <si>
+    <t>Cuota 1 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
+  </si>
+  <si>
+    <t>Honorarios y aportes al Sr. Perito Mario Ruben Patitucci</t>
+  </si>
+  <si>
+    <t>Aportes Dr. Ezequiel Sarro - Sr abogado</t>
+  </si>
+  <si>
+    <t>Ezequiel Sarro - Sr Abogado - Presetacion escrito</t>
   </si>
 </sst>
 </file>
@@ -1628,12 +1634,94 @@
     <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1652,12 +1740,6 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1679,81 +1761,6 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1775,6 +1782,12 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1784,13 +1797,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2238,16 +2244,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K99"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2262,23 +2268,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="209"/>
+      <c r="D2" s="209"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="210"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="211"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="221">
+      <c r="E3" s="212">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="221"/>
-      <c r="G3" s="221"/>
-      <c r="H3" s="222"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="213"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2314,7 +2320,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2357,14 +2363,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="219"/>
-      <c r="B12" s="186"/>
-      <c r="C12" s="186"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="186"/>
-      <c r="H12" s="220"/>
+      <c r="A12" s="194"/>
+      <c r="B12" s="195"/>
+      <c r="C12" s="195"/>
+      <c r="D12" s="195"/>
+      <c r="E12" s="195"/>
+      <c r="F12" s="195"/>
+      <c r="G12" s="195"/>
+      <c r="H12" s="196"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2376,21 +2382,21 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="223" t="s">
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="197" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="223"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="223"/>
-      <c r="G14" s="223"/>
-      <c r="H14" s="223"/>
+      <c r="B14" s="197"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
+      <c r="F14" s="197"/>
+      <c r="G14" s="197"/>
+      <c r="H14" s="197"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="172" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B15" s="137"/>
       <c r="C15" s="137"/>
@@ -2399,7 +2405,7 @@
       <c r="F15" s="137"/>
       <c r="G15" s="137"/>
       <c r="H15" s="73">
-        <v>417468.99</v>
+        <v>347680.6</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2413,7 +2419,7 @@
       <c r="F16" s="137"/>
       <c r="G16" s="137"/>
       <c r="H16" s="73">
-        <v>-65751.37</v>
+        <v>-54759.7</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -2428,7 +2434,7 @@
       <c r="F17" s="137"/>
       <c r="G17" s="137"/>
       <c r="H17" s="73">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -2444,25 +2450,25 @@
       <c r="G18" s="137"/>
       <c r="H18" s="69">
         <f>SUM(H15:H17)</f>
-        <v>351718</v>
+        <v>292920.99999999994</v>
       </c>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="215" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="215"/>
-      <c r="C19" s="215"/>
-      <c r="D19" s="215"/>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
-      <c r="G19" s="215"/>
-      <c r="H19" s="215"/>
-    </row>
-    <row r="20" spans="1:9">
+    <row r="19" spans="1:9" hidden="1">
+      <c r="A19" s="190" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="190"/>
+      <c r="C19" s="190"/>
+      <c r="D19" s="190"/>
+      <c r="E19" s="190"/>
+      <c r="F19" s="190"/>
+      <c r="G19" s="190"/>
+      <c r="H19" s="190"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="172" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B20" s="137"/>
       <c r="C20" s="137"/>
@@ -2471,12 +2477,12 @@
       <c r="F20" s="137"/>
       <c r="G20" s="137"/>
       <c r="H20" s="73">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" hidden="1">
       <c r="A21" s="172" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B21" s="137"/>
       <c r="C21" s="137"/>
@@ -2485,10 +2491,10 @@
       <c r="F21" s="137"/>
       <c r="G21" s="137"/>
       <c r="H21" s="73">
-        <v>4519.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" hidden="1">
       <c r="A22" s="172" t="s">
         <v>73</v>
       </c>
@@ -2500,24 +2506,24 @@
       <c r="G22" s="137"/>
       <c r="H22" s="69">
         <f>SUM(H20:H21)</f>
-        <v>56519.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="214" t="s">
+      <c r="A23" s="189" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="214"/>
-      <c r="C23" s="214"/>
-      <c r="D23" s="214"/>
-      <c r="E23" s="214"/>
-      <c r="F23" s="214"/>
-      <c r="G23" s="214"/>
-      <c r="H23" s="214"/>
+      <c r="B23" s="189"/>
+      <c r="C23" s="189"/>
+      <c r="D23" s="189"/>
+      <c r="E23" s="189"/>
+      <c r="F23" s="189"/>
+      <c r="G23" s="189"/>
+      <c r="H23" s="189"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B24" s="137"/>
       <c r="C24" s="137"/>
@@ -2526,7 +2532,8 @@
       <c r="F24" s="137"/>
       <c r="G24" s="137"/>
       <c r="H24" s="73">
-        <v>32000</v>
+        <f>17000+32000</f>
+        <v>49000</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2551,20 +2558,20 @@
       <c r="G26" s="137"/>
       <c r="H26" s="69">
         <f>SUM(H24:H25)</f>
-        <v>32000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="210" t="s">
+      <c r="A27" s="201" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="210"/>
-      <c r="C27" s="210"/>
-      <c r="D27" s="210"/>
-      <c r="E27" s="210"/>
-      <c r="F27" s="210"/>
-      <c r="G27" s="210"/>
-      <c r="H27" s="210"/>
+      <c r="B27" s="201"/>
+      <c r="C27" s="201"/>
+      <c r="D27" s="201"/>
+      <c r="E27" s="201"/>
+      <c r="F27" s="201"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="201"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="172"/>
@@ -2587,13 +2594,13 @@
       <c r="F29" s="137"/>
       <c r="G29" s="137"/>
       <c r="H29" s="73">
-        <f>41955.11+1661.16+14950.47</f>
-        <v>58566.740000000005</v>
+        <f>18786.1+2087.34+47841.49</f>
+        <v>68714.929999999993</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="137" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B30" s="137"/>
       <c r="C30" s="137"/>
@@ -2617,24 +2624,24 @@
       <c r="G31" s="137"/>
       <c r="H31" s="69">
         <f>SUM(H28:H30)</f>
-        <v>58566.740000000005</v>
+        <v>68714.929999999993</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="210" t="s">
+      <c r="A32" s="201" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="210"/>
-      <c r="C32" s="210"/>
-      <c r="D32" s="210"/>
-      <c r="E32" s="210"/>
-      <c r="F32" s="210"/>
-      <c r="G32" s="210"/>
-      <c r="H32" s="210"/>
+      <c r="B32" s="201"/>
+      <c r="C32" s="201"/>
+      <c r="D32" s="201"/>
+      <c r="E32" s="201"/>
+      <c r="F32" s="201"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="201"/>
     </row>
     <row r="33" spans="1:11" ht="14.25" customHeight="1">
       <c r="A33" s="137" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B33" s="137"/>
       <c r="C33" s="137"/>
@@ -2643,7 +2650,7 @@
       <c r="F33" s="137"/>
       <c r="G33" s="137"/>
       <c r="H33" s="73">
-        <v>1078660.6200000001</v>
+        <v>1080249.04</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2657,7 +2664,7 @@
       <c r="F34" s="137"/>
       <c r="G34" s="137"/>
       <c r="H34" s="73">
-        <v>71134.429999999993</v>
+        <v>42958.13</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2672,20 +2679,20 @@
       <c r="G35" s="137"/>
       <c r="H35" s="175">
         <f>SUM(H33:H34)</f>
-        <v>1149795.05</v>
+        <v>1123207.17</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="223" t="s">
+      <c r="A36" s="197" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="223"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="223"/>
+      <c r="B36" s="197"/>
+      <c r="C36" s="197"/>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="197"/>
+      <c r="H36" s="197"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="80" t="s">
@@ -2698,12 +2705,12 @@
       <c r="F37" s="137"/>
       <c r="G37" s="137"/>
       <c r="H37" s="73">
-        <v>85000</v>
+        <v>93200</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="80" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="137"/>
       <c r="C38" s="137"/>
@@ -2712,7 +2719,7 @@
       <c r="F38" s="137"/>
       <c r="G38" s="137"/>
       <c r="H38" s="73">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="I38" s="7"/>
     </row>
@@ -2727,7 +2734,7 @@
       <c r="F39" s="137"/>
       <c r="G39" s="137"/>
       <c r="H39" s="73">
-        <v>24285.72</v>
+        <v>25300</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2746,7 +2753,7 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="137" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B41" s="137"/>
       <c r="C41" s="137"/>
@@ -2755,7 +2762,7 @@
       <c r="F41" s="137"/>
       <c r="G41" s="137"/>
       <c r="H41" s="73">
-        <v>0</v>
+        <v>413700</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2770,20 +2777,20 @@
       <c r="G42" s="137"/>
       <c r="H42" s="69">
         <f>SUM(H37:H41)</f>
-        <v>374285.72</v>
+        <v>597200</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="223" t="s">
+      <c r="A43" s="197" t="s">
         <v>130</v>
       </c>
-      <c r="B43" s="223"/>
-      <c r="C43" s="223"/>
-      <c r="D43" s="223"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="223"/>
+      <c r="B43" s="197"/>
+      <c r="C43" s="197"/>
+      <c r="D43" s="197"/>
+      <c r="E43" s="197"/>
+      <c r="F43" s="197"/>
+      <c r="G43" s="197"/>
+      <c r="H43" s="197"/>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="137" t="s">
@@ -2799,7 +2806,7 @@
         <v>189700</v>
       </c>
       <c r="J44" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2833,16 +2840,16 @@
       <c r="K46" s="7"/>
     </row>
     <row r="47" spans="1:11" s="6" customFormat="1">
-      <c r="A47" s="224" t="s">
+      <c r="A47" s="198" t="s">
         <v>131</v>
       </c>
-      <c r="B47" s="225"/>
-      <c r="C47" s="225"/>
-      <c r="D47" s="225"/>
-      <c r="E47" s="225"/>
-      <c r="F47" s="225"/>
-      <c r="G47" s="225"/>
-      <c r="H47" s="226"/>
+      <c r="B47" s="199"/>
+      <c r="C47" s="199"/>
+      <c r="D47" s="199"/>
+      <c r="E47" s="199"/>
+      <c r="F47" s="199"/>
+      <c r="G47" s="199"/>
+      <c r="H47" s="200"/>
     </row>
     <row r="48" spans="1:11" s="6" customFormat="1">
       <c r="A48" s="80" t="s">
@@ -2875,20 +2882,20 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1">
-      <c r="A50" s="223" t="s">
+      <c r="A50" s="197" t="s">
         <v>132</v>
       </c>
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
-      <c r="D50" s="223"/>
-      <c r="E50" s="223"/>
-      <c r="F50" s="223"/>
-      <c r="G50" s="223"/>
-      <c r="H50" s="223"/>
+      <c r="B50" s="197"/>
+      <c r="C50" s="197"/>
+      <c r="D50" s="197"/>
+      <c r="E50" s="197"/>
+      <c r="F50" s="197"/>
+      <c r="G50" s="197"/>
+      <c r="H50" s="197"/>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1">
       <c r="A51" s="80" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B51" s="80"/>
       <c r="C51" s="80"/>
@@ -2897,32 +2904,39 @@
       <c r="F51" s="80"/>
       <c r="G51" s="80"/>
       <c r="H51" s="73">
-        <v>100000</v>
+        <f>97952+30365</f>
+        <v>128317</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1">
-      <c r="A52" s="80"/>
+      <c r="A52" s="80" t="s">
+        <v>158</v>
+      </c>
       <c r="B52" s="80"/>
       <c r="C52" s="80"/>
       <c r="D52" s="80"/>
       <c r="E52" s="80"/>
       <c r="F52" s="80"/>
       <c r="G52" s="80"/>
-      <c r="H52" s="73"/>
+      <c r="H52" s="73">
+        <v>100000</v>
+      </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1">
-      <c r="A53" s="80"/>
+      <c r="A53" s="80" t="s">
+        <v>157</v>
+      </c>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
       <c r="D53" s="80"/>
       <c r="E53" s="80"/>
       <c r="F53" s="80"/>
       <c r="G53" s="80"/>
-      <c r="H53" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="H53" s="73">
+        <v>49750</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="80" t="s">
         <v>74</v>
       </c>
@@ -2934,19 +2948,19 @@
       <c r="G54" s="80"/>
       <c r="H54" s="69">
         <f>SUM(H51:H53)</f>
-        <v>100000</v>
+        <v>278067</v>
       </c>
       <c r="I54" s="60"/>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A55" s="224"/>
-      <c r="B55" s="225"/>
-      <c r="C55" s="225"/>
-      <c r="D55" s="225"/>
-      <c r="E55" s="225"/>
-      <c r="F55" s="225"/>
-      <c r="G55" s="225"/>
-      <c r="H55" s="226"/>
+      <c r="A55" s="198"/>
+      <c r="B55" s="199"/>
+      <c r="C55" s="199"/>
+      <c r="D55" s="199"/>
+      <c r="E55" s="199"/>
+      <c r="F55" s="199"/>
+      <c r="G55" s="199"/>
+      <c r="H55" s="200"/>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
       <c r="A56" s="81"/>
@@ -2997,49 +3011,49 @@
       <c r="G59" s="203"/>
       <c r="H59" s="162">
         <f>H54</f>
-        <v>100000</v>
+        <v>278067</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A60" s="205"/>
-      <c r="B60" s="205"/>
-      <c r="C60" s="205"/>
-      <c r="D60" s="205"/>
-      <c r="E60" s="205"/>
-      <c r="F60" s="205"/>
-      <c r="G60" s="205"/>
-      <c r="H60" s="205"/>
+      <c r="A60" s="207"/>
+      <c r="B60" s="207"/>
+      <c r="C60" s="207"/>
+      <c r="D60" s="207"/>
+      <c r="E60" s="207"/>
+      <c r="F60" s="207"/>
+      <c r="G60" s="207"/>
+      <c r="H60" s="207"/>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A61" s="206"/>
-      <c r="B61" s="206"/>
-      <c r="C61" s="206"/>
-      <c r="D61" s="206"/>
-      <c r="E61" s="206"/>
-      <c r="F61" s="206"/>
-      <c r="G61" s="206"/>
-      <c r="H61" s="206"/>
+      <c r="A61" s="208"/>
+      <c r="B61" s="208"/>
+      <c r="C61" s="208"/>
+      <c r="D61" s="208"/>
+      <c r="E61" s="208"/>
+      <c r="F61" s="208"/>
+      <c r="G61" s="208"/>
+      <c r="H61" s="208"/>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="204" t="s">
+      <c r="A62" s="206" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="204"/>
-      <c r="C62" s="204"/>
-      <c r="D62" s="204"/>
-      <c r="E62" s="204"/>
-      <c r="F62" s="204"/>
-      <c r="G62" s="204"/>
+      <c r="B62" s="206"/>
+      <c r="C62" s="206"/>
+      <c r="D62" s="206"/>
+      <c r="E62" s="206"/>
+      <c r="F62" s="206"/>
+      <c r="G62" s="206"/>
       <c r="H62" s="163"/>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A63" s="216"/>
-      <c r="B63" s="217"/>
-      <c r="C63" s="217"/>
-      <c r="D63" s="217"/>
-      <c r="E63" s="217"/>
-      <c r="F63" s="217"/>
-      <c r="G63" s="218"/>
+      <c r="A63" s="191"/>
+      <c r="B63" s="192"/>
+      <c r="C63" s="192"/>
+      <c r="D63" s="192"/>
+      <c r="E63" s="192"/>
+      <c r="F63" s="192"/>
+      <c r="G63" s="193"/>
       <c r="H63" s="73"/>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
@@ -3068,89 +3082,89 @@
       <c r="H65" s="129"/>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A66" s="193" t="s">
+      <c r="A66" s="204" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="194"/>
-      <c r="C66" s="194"/>
-      <c r="D66" s="194"/>
-      <c r="E66" s="194"/>
-      <c r="F66" s="194"/>
-      <c r="G66" s="194"/>
+      <c r="B66" s="205"/>
+      <c r="C66" s="205"/>
+      <c r="D66" s="205"/>
+      <c r="E66" s="205"/>
+      <c r="F66" s="205"/>
+      <c r="G66" s="205"/>
       <c r="H66" s="130">
         <f>H64</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A67" s="211" t="s">
+      <c r="A67" s="186" t="s">
         <v>87</v>
       </c>
-      <c r="B67" s="212"/>
-      <c r="C67" s="212"/>
-      <c r="D67" s="212"/>
-      <c r="E67" s="212"/>
-      <c r="F67" s="212"/>
-      <c r="G67" s="213"/>
+      <c r="B67" s="187"/>
+      <c r="C67" s="187"/>
+      <c r="D67" s="187"/>
+      <c r="E67" s="187"/>
+      <c r="F67" s="187"/>
+      <c r="G67" s="188"/>
       <c r="H67" s="130"/>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="211" t="s">
+      <c r="A68" s="186" t="s">
         <v>92</v>
       </c>
-      <c r="B68" s="212"/>
-      <c r="C68" s="212"/>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
-      <c r="F68" s="212"/>
-      <c r="G68" s="213"/>
+      <c r="B68" s="187"/>
+      <c r="C68" s="187"/>
+      <c r="D68" s="187"/>
+      <c r="E68" s="187"/>
+      <c r="F68" s="187"/>
+      <c r="G68" s="188"/>
       <c r="H68" s="130"/>
     </row>
-    <row r="69" spans="1:11" ht="18">
-      <c r="A69" s="193" t="s">
+    <row r="69" spans="1:11" ht="18.75">
+      <c r="A69" s="204" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="194"/>
-      <c r="C69" s="194"/>
-      <c r="D69" s="194"/>
-      <c r="E69" s="194"/>
-      <c r="F69" s="194"/>
-      <c r="G69" s="194"/>
+      <c r="B69" s="205"/>
+      <c r="C69" s="205"/>
+      <c r="D69" s="205"/>
+      <c r="E69" s="205"/>
+      <c r="F69" s="205"/>
+      <c r="G69" s="205"/>
       <c r="H69" s="130">
         <f>H26+H35+H42+H46+H49+H31+H18+H22</f>
-        <v>2283892.2599999998</v>
+        <v>2392050.1</v>
       </c>
       <c r="J69" s="171"/>
       <c r="K69" s="142"/>
     </row>
-    <row r="70" spans="1:11" ht="18">
-      <c r="A70" s="199" t="s">
+    <row r="70" spans="1:11" ht="18.75">
+      <c r="A70" s="225" t="s">
         <v>120</v>
       </c>
-      <c r="B70" s="200"/>
-      <c r="C70" s="200"/>
-      <c r="D70" s="200"/>
-      <c r="E70" s="200"/>
-      <c r="F70" s="200"/>
-      <c r="G70" s="201"/>
+      <c r="B70" s="226"/>
+      <c r="C70" s="226"/>
+      <c r="D70" s="226"/>
+      <c r="E70" s="226"/>
+      <c r="F70" s="226"/>
+      <c r="G70" s="227"/>
       <c r="H70" s="131">
         <f>H67+H69</f>
-        <v>2283892.2599999998</v>
+        <v>2392050.1</v>
       </c>
       <c r="I70" s="126"/>
-      <c r="J70" s="185"/>
-      <c r="K70" s="185"/>
-    </row>
-    <row r="71" spans="1:11" ht="18">
-      <c r="A71" s="199" t="s">
+      <c r="J70" s="214"/>
+      <c r="K70" s="214"/>
+    </row>
+    <row r="71" spans="1:11" ht="18.75">
+      <c r="A71" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="B71" s="200"/>
-      <c r="C71" s="200"/>
-      <c r="D71" s="200"/>
-      <c r="E71" s="200"/>
-      <c r="F71" s="200"/>
-      <c r="G71" s="201"/>
+      <c r="B71" s="226"/>
+      <c r="C71" s="226"/>
+      <c r="D71" s="226"/>
+      <c r="E71" s="226"/>
+      <c r="F71" s="226"/>
+      <c r="G71" s="227"/>
       <c r="H71" s="132">
         <f>H68+H66</f>
         <v>0</v>
@@ -3158,38 +3172,38 @@
       <c r="J71" s="142"/>
     </row>
     <row r="72" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A72" s="197" t="s">
+      <c r="A72" s="223" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="198"/>
-      <c r="C72" s="198"/>
-      <c r="D72" s="198"/>
-      <c r="E72" s="198"/>
-      <c r="F72" s="198"/>
-      <c r="G72" s="198"/>
+      <c r="B72" s="224"/>
+      <c r="C72" s="224"/>
+      <c r="D72" s="224"/>
+      <c r="E72" s="224"/>
+      <c r="F72" s="224"/>
+      <c r="G72" s="224"/>
       <c r="H72" s="133">
         <f>H69+H66</f>
-        <v>2283892.2599999998</v>
+        <v>2392050.1</v>
       </c>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" spans="1:11" ht="18" hidden="1">
-      <c r="A73" s="195" t="s">
+    <row r="73" spans="1:11" ht="18.75" hidden="1">
+      <c r="A73" s="221" t="s">
         <v>17</v>
       </c>
-      <c r="B73" s="196"/>
-      <c r="C73" s="196"/>
-      <c r="D73" s="196"/>
-      <c r="E73" s="196"/>
-      <c r="F73" s="196"/>
-      <c r="G73" s="196"/>
+      <c r="B73" s="222"/>
+      <c r="C73" s="222"/>
+      <c r="D73" s="222"/>
+      <c r="E73" s="222"/>
+      <c r="F73" s="222"/>
+      <c r="G73" s="222"/>
       <c r="H73" s="134">
         <f>H58</f>
         <v>0</v>
       </c>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:11" ht="18" hidden="1">
+    <row r="74" spans="1:11" ht="18.75" hidden="1">
       <c r="A74" s="135"/>
       <c r="B74" s="135"/>
       <c r="C74" s="135"/>
@@ -3200,7 +3214,7 @@
       <c r="H74" s="136"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:11" ht="18" hidden="1">
+    <row r="75" spans="1:11" ht="18.75" hidden="1">
       <c r="A75" s="135"/>
       <c r="B75" s="135"/>
       <c r="C75" s="135"/>
@@ -3211,7 +3225,7 @@
       <c r="H75" s="136"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:11" ht="18" hidden="1">
+    <row r="76" spans="1:11" ht="18.75" hidden="1">
       <c r="A76" s="135"/>
       <c r="B76" s="135"/>
       <c r="C76" s="135"/>
@@ -3232,19 +3246,19 @@
       <c r="G77" s="137"/>
       <c r="H77" s="137"/>
     </row>
-    <row r="78" spans="1:11" ht="18">
-      <c r="A78" s="190" t="s">
+    <row r="78" spans="1:11" ht="18.75">
+      <c r="A78" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="191"/>
-      <c r="C78" s="191"/>
-      <c r="D78" s="191"/>
-      <c r="E78" s="191"/>
-      <c r="F78" s="191"/>
-      <c r="G78" s="191"/>
-      <c r="H78" s="192"/>
-    </row>
-    <row r="79" spans="1:11" ht="18">
+      <c r="B78" s="219"/>
+      <c r="C78" s="219"/>
+      <c r="D78" s="219"/>
+      <c r="E78" s="219"/>
+      <c r="F78" s="219"/>
+      <c r="G78" s="219"/>
+      <c r="H78" s="220"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75">
       <c r="A79" s="138" t="s">
         <v>12</v>
       </c>
@@ -3255,12 +3269,12 @@
       <c r="F79" s="139"/>
       <c r="G79" s="139"/>
       <c r="H79" s="140">
-        <v>4813257.659039462</v>
+        <v>7329447.2949116919</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="81" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B80" s="82"/>
       <c r="C80" s="82"/>
@@ -3270,7 +3284,7 @@
       <c r="G80" s="82"/>
       <c r="H80" s="141">
         <f>Planilla!G32</f>
-        <v>4691108.2961447304</v>
+        <v>1983592.6250439996</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3285,7 +3299,7 @@
       <c r="G81" s="79"/>
       <c r="H81" s="179">
         <f>-(H72)</f>
-        <v>-2283892.2599999998</v>
+        <v>-2392050.1</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3300,13 +3314,13 @@
       <c r="G82" s="79"/>
       <c r="H82" s="179">
         <f>-H59</f>
-        <v>-100000</v>
+        <v>-278067</v>
       </c>
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B83" s="79"/>
       <c r="C83" s="79"/>
@@ -3330,7 +3344,8 @@
       <c r="F84" s="79"/>
       <c r="G84" s="79"/>
       <c r="H84" s="121">
-        <v>75293.599727499997</v>
+        <f>180000-H83</f>
+        <v>46320</v>
       </c>
       <c r="I84" s="142"/>
       <c r="J84" s="7"/>
@@ -3347,7 +3362,7 @@
       <c r="G85" s="4"/>
       <c r="H85" s="98"/>
     </row>
-    <row r="86" spans="1:11" ht="18">
+    <row r="86" spans="1:11" ht="18.75">
       <c r="A86" s="22" t="s">
         <v>11</v>
       </c>
@@ -3359,23 +3374,23 @@
       <c r="G86" s="23"/>
       <c r="H86" s="84">
         <f>SUM(H79:H85)</f>
-        <v>7329447.2949116919</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="15" thickBot="1"/>
-    <row r="88" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A88" s="187" t="s">
+        <v>6822922.8199556917</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="88" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A88" s="215" t="s">
         <v>97</v>
       </c>
-      <c r="B88" s="188"/>
-      <c r="C88" s="188"/>
-      <c r="D88" s="188"/>
-      <c r="E88" s="188"/>
-      <c r="F88" s="188"/>
-      <c r="G88" s="188"/>
-      <c r="H88" s="189"/>
-    </row>
-    <row r="89" spans="1:11" ht="15.6">
+      <c r="B88" s="216"/>
+      <c r="C88" s="216"/>
+      <c r="D88" s="216"/>
+      <c r="E88" s="216"/>
+      <c r="F88" s="216"/>
+      <c r="G88" s="216"/>
+      <c r="H88" s="217"/>
+    </row>
+    <row r="89" spans="1:11" ht="15.75">
       <c r="A89" s="87" t="s">
         <v>12</v>
       </c>
@@ -3437,47 +3452,60 @@
       </c>
     </row>
     <row r="96" spans="1:11" hidden="1">
-      <c r="A96" s="186"/>
-      <c r="B96" s="186"/>
-      <c r="C96" s="186"/>
-      <c r="D96" s="186"/>
-      <c r="E96" s="186"/>
-      <c r="F96" s="186"/>
-      <c r="G96" s="186"/>
-      <c r="H96" s="186"/>
+      <c r="A96" s="195"/>
+      <c r="B96" s="195"/>
+      <c r="C96" s="195"/>
+      <c r="D96" s="195"/>
+      <c r="E96" s="195"/>
+      <c r="F96" s="195"/>
+      <c r="G96" s="195"/>
+      <c r="H96" s="195"/>
     </row>
     <row r="97" spans="1:8" hidden="1">
-      <c r="A97" s="186"/>
-      <c r="B97" s="186"/>
-      <c r="C97" s="186"/>
-      <c r="D97" s="186"/>
-      <c r="E97" s="186"/>
-      <c r="F97" s="186"/>
-      <c r="G97" s="186"/>
-      <c r="H97" s="186"/>
+      <c r="A97" s="195"/>
+      <c r="B97" s="195"/>
+      <c r="C97" s="195"/>
+      <c r="D97" s="195"/>
+      <c r="E97" s="195"/>
+      <c r="F97" s="195"/>
+      <c r="G97" s="195"/>
+      <c r="H97" s="195"/>
     </row>
     <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="186"/>
-      <c r="B98" s="186"/>
-      <c r="C98" s="186"/>
-      <c r="D98" s="186"/>
-      <c r="E98" s="186"/>
-      <c r="F98" s="186"/>
-      <c r="G98" s="186"/>
-      <c r="H98" s="186"/>
+      <c r="A98" s="195"/>
+      <c r="B98" s="195"/>
+      <c r="C98" s="195"/>
+      <c r="D98" s="195"/>
+      <c r="E98" s="195"/>
+      <c r="F98" s="195"/>
+      <c r="G98" s="195"/>
+      <c r="H98" s="195"/>
     </row>
     <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="186"/>
-      <c r="B99" s="186"/>
-      <c r="C99" s="186"/>
-      <c r="D99" s="186"/>
-      <c r="E99" s="186"/>
-      <c r="F99" s="186"/>
-      <c r="G99" s="186"/>
-      <c r="H99" s="186"/>
+      <c r="A99" s="195"/>
+      <c r="B99" s="195"/>
+      <c r="C99" s="195"/>
+      <c r="D99" s="195"/>
+      <c r="E99" s="195"/>
+      <c r="F99" s="195"/>
+      <c r="G99" s="195"/>
+      <c r="H99" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A96:H99"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A60:H61"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="J70:K70"/>
     <mergeCell ref="A68:G68"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
@@ -3494,19 +3522,6 @@
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A60:H61"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="A96:H99"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A70:G70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3517,24 +3532,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.77734375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3547,12 +3562,12 @@
       </c>
       <c r="F1" s="105" t="str">
         <f>RESUMEN!F8</f>
-        <v>MARZO</v>
+        <v>ABRIL</v>
       </c>
       <c r="G1" s="106"/>
       <c r="H1" s="104" t="str">
         <f>RESUMEN!G8</f>
-        <v>VTO: 17/04</v>
+        <v>VTO: 15/05</v>
       </c>
       <c r="I1" s="103"/>
       <c r="J1" s="103"/>
@@ -3595,51 +3610,51 @@
       <c r="I3" s="117"/>
       <c r="J3" s="117"/>
       <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="61" t="s">
+      <c r="L3" s="61" t="s">
         <v>77</v>
       </c>
+      <c r="M3" s="61"/>
       <c r="N3" s="61"/>
       <c r="O3" s="61"/>
     </row>
     <row r="4" spans="1:17" ht="18.75" customHeight="1">
       <c r="A4" s="118"/>
       <c r="B4" s="119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
       <c r="E4" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="239">
-        <f>106000-330-20+2</f>
-        <v>105652</v>
+      <c r="F4" s="185">
+        <f>278067+10000+9000-3000-520+225+12</f>
+        <v>293784</v>
       </c>
       <c r="G4" s="117"/>
       <c r="H4" s="117"/>
       <c r="I4" s="117"/>
       <c r="J4" s="117"/>
       <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="61" t="s">
+      <c r="L4" s="61" t="s">
         <v>76</v>
       </c>
+      <c r="M4" s="61"/>
       <c r="N4" s="61"/>
       <c r="O4" s="61"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="228">
+      <c r="B5" s="229">
         <f>C2</f>
         <v>2283892.2599999998</v>
       </c>
-      <c r="C5" s="228"/>
+      <c r="C5" s="229"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="237">
-        <v>100000</v>
-      </c>
-      <c r="F5" s="238"/>
+      <c r="E5" s="235">
+        <v>278067</v>
+      </c>
+      <c r="F5" s="236"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3652,13 +3667,13 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="230"/>
-      <c r="C6" s="231"/>
+      <c r="B6" s="231"/>
+      <c r="C6" s="232"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="230" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="231"/>
+      <c r="E6" s="231" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="232"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
@@ -3671,11 +3686,11 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="228"/>
-      <c r="C7" s="228"/>
+      <c r="B7" s="229"/>
+      <c r="C7" s="229"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="233"/>
+      <c r="E7" s="233"/>
+      <c r="F7" s="234"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
@@ -3706,13 +3721,13 @@
         <v>16</v>
       </c>
       <c r="G8" s="112" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H8" s="112" t="s">
         <v>63</v>
       </c>
       <c r="I8" s="112" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J8" s="112" t="s">
         <v>64</v>
@@ -3727,7 +3742,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="109" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O8" s="113" t="s">
         <v>8</v>
@@ -3750,11 +3765,10 @@
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>205818.87536999999</v>
+        <v>-103223.45747000005</v>
       </c>
       <c r="G9" s="176">
-        <f>F9+200000</f>
-        <v>405818.87537000002</v>
+        <v>0</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
@@ -3766,11 +3780,11 @@
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
-        <v>200000.00000000003</v>
+        <v>103223.45747000005</v>
       </c>
       <c r="K9" s="68">
         <f>F$4*E9</f>
-        <v>4278.9059999999999</v>
+        <v>11898.252</v>
       </c>
       <c r="L9" s="68">
         <f>E$7*E9</f>
@@ -3786,7 +3800,7 @@
       </c>
       <c r="O9" s="183">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>-103223.45747000005</v>
+        <v>1172.4310599999444</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3804,11 +3818,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>329310.20059199998</v>
+        <v>154842.46804799998</v>
       </c>
       <c r="G10" s="176">
         <f>F10</f>
-        <v>329310.20059199998</v>
+        <v>154842.46804799998</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -3824,7 +3838,7 @@
       </c>
       <c r="K10" s="24">
         <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
-        <v>6846.2495999999992</v>
+        <v>19037.2032</v>
       </c>
       <c r="L10" s="68">
         <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
@@ -3840,7 +3854,7 @@
       </c>
       <c r="O10" s="183">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>154842.46804799998</v>
+        <v>167033.42164799996</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
@@ -3860,11 +3874,11 @@
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>244949.87142800001</v>
+        <v>115176.03333199999</v>
       </c>
       <c r="G11" s="176">
         <f>F11</f>
-        <v>244949.87142800001</v>
+        <v>115176.03333199999</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -3880,7 +3894,7 @@
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>5092.4264000000003</v>
+        <v>14160.388800000001</v>
       </c>
       <c r="L11" s="68">
         <f t="shared" si="3"/>
@@ -3896,7 +3910,7 @@
       </c>
       <c r="O11" s="183">
         <f t="shared" si="6"/>
-        <v>115176.03333199999</v>
+        <v>124243.995732</v>
       </c>
       <c r="P11" s="171"/>
     </row>
@@ -3917,16 +3931,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="147">
-        <v>4531867.5137583734</v>
+        <v>4827387.2296774341</v>
       </c>
       <c r="G12" s="177"/>
       <c r="H12" s="148">
         <f t="shared" si="0"/>
-        <v>4531867.5137583734</v>
+        <v>4827387.2296774341</v>
       </c>
       <c r="I12" s="148">
         <f t="shared" si="7"/>
-        <v>167679.09800905985</v>
+        <v>178613.32749806507</v>
       </c>
       <c r="J12" s="148">
         <f t="shared" si="1"/>
@@ -3934,7 +3948,7 @@
       </c>
       <c r="K12" s="148">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>15717.444</v>
       </c>
       <c r="L12" s="148">
         <f t="shared" si="3"/>
@@ -3950,7 +3964,7 @@
       </c>
       <c r="O12" s="184">
         <f t="shared" si="6"/>
-        <v>4827387.2296774341</v>
+        <v>5143906.2370854998</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -3968,11 +3982,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>195654.98029000001</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="G13" s="176">
         <f>F13</f>
-        <v>195654.98029000001</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -3988,7 +4002,7 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>11310.683999999999</v>
       </c>
       <c r="L13" s="68">
         <f t="shared" si="3"/>
@@ -4004,7 +4018,7 @@
       </c>
       <c r="O13" s="183">
         <f t="shared" si="6"/>
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4024,11 +4038,10 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
       <c r="G14" s="176">
-        <f>F14</f>
-        <v>182441.91668600001</v>
+        <v>85800</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -4040,11 +4053,11 @@
       </c>
       <c r="J14" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.361066000012215</v>
       </c>
       <c r="K14" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>10546.845600000001</v>
       </c>
       <c r="L14" s="68">
         <f t="shared" si="3"/>
@@ -4060,7 +4073,7 @@
       </c>
       <c r="O14" s="183">
         <f t="shared" si="6"/>
-        <v>85784.638933999988</v>
+        <v>92523.216667999979</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4071,7 +4084,7 @@
         <v>46</v>
       </c>
       <c r="C15" s="93" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D15" s="92" t="s">
         <v>106</v>
@@ -4080,11 +4093,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>203330.13136200001</v>
+        <v>98927.13236399999</v>
       </c>
       <c r="G15" s="176">
         <f>F15</f>
-        <v>203330.13136200001</v>
+        <v>98927.13236399999</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -4100,7 +4113,7 @@
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>12162.6576</v>
       </c>
       <c r="L15" s="68">
         <f t="shared" si="3"/>
@@ -4115,7 +4128,7 @@
       </c>
       <c r="O15" s="183">
         <f t="shared" si="6"/>
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="Q15" s="180"/>
     </row>
@@ -4136,11 +4149,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>271884.19338999997</v>
+        <v>127840.61790999999</v>
       </c>
       <c r="G16" s="176">
         <f>F16</f>
-        <v>271884.19338999997</v>
+        <v>127840.61790999999</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -4156,7 +4169,7 @@
       </c>
       <c r="K16" s="24">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>15717.444</v>
       </c>
       <c r="L16" s="68">
         <f t="shared" si="3"/>
@@ -4172,7 +4185,7 @@
       </c>
       <c r="O16" s="183">
         <f t="shared" si="6"/>
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="Q16" s="180"/>
     </row>
@@ -4193,11 +4206,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>398549.19485072995</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="G17" s="176">
         <f>F17</f>
-        <v>398549.19485072995</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
@@ -4213,7 +4226,7 @@
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>11310.683999999999</v>
       </c>
       <c r="L17" s="68">
         <f t="shared" si="3"/>
@@ -4229,7 +4242,7 @@
       </c>
       <c r="O17" s="183">
         <f t="shared" si="6"/>
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="Q17" s="180"/>
     </row>
@@ -4248,27 +4261,27 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>313378.30951486056</v>
+        <v>208542.94590091039</v>
       </c>
       <c r="G18" s="176">
-        <f>RESUMEN!H40+RESUMEN!H37+RESUMEN!H45</f>
-        <v>195000</v>
+        <f>RESUMEN!H37+RESUMEN!H40+RESUMEN!H45+20000</f>
+        <v>223200</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>118378.30951486056</v>
+        <v>0</v>
       </c>
       <c r="I18" s="68">
         <f t="shared" si="7"/>
-        <v>4379.9974520498417</v>
+        <v>0</v>
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14657.054099089612</v>
       </c>
       <c r="K18" s="68">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>10546.845600000001</v>
       </c>
       <c r="L18" s="68">
         <f t="shared" si="3"/>
@@ -4284,7 +4297,7 @@
       </c>
       <c r="O18" s="183">
         <f t="shared" si="6"/>
-        <v>208542.94590091039</v>
+        <v>77881.52363491038</v>
       </c>
       <c r="Q18" s="180"/>
     </row>
@@ -4305,16 +4318,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="147">
-        <v>3181542.9629749977</v>
+        <v>3398187.1849690727</v>
       </c>
       <c r="G19" s="177"/>
       <c r="H19" s="148">
         <f t="shared" si="0"/>
-        <v>3181542.9629749977</v>
+        <v>3398187.1849690727</v>
       </c>
       <c r="I19" s="148">
         <f t="shared" si="7"/>
-        <v>117717.08963007493</v>
+        <v>125732.9258438557</v>
       </c>
       <c r="J19" s="148">
         <f t="shared" si="1"/>
@@ -4322,7 +4335,7 @@
       </c>
       <c r="K19" s="148">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>12162.6576</v>
       </c>
       <c r="L19" s="148">
         <f t="shared" si="3"/>
@@ -4338,7 +4351,7 @@
       </c>
       <c r="O19" s="184">
         <f t="shared" si="6"/>
-        <v>3398187.1849690727</v>
+        <v>3630635.9079769286</v>
       </c>
       <c r="Q19" s="180"/>
     </row>
@@ -4359,11 +4372,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>271884.19338999997</v>
+        <v>127840.61790999999</v>
       </c>
       <c r="G20" s="176">
         <f>F20</f>
-        <v>271884.19338999997</v>
+        <v>127840.61790999999</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -4379,7 +4392,7 @@
       </c>
       <c r="K20" s="24">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>15717.444</v>
       </c>
       <c r="L20" s="68">
         <f t="shared" si="3"/>
@@ -4395,7 +4408,7 @@
       </c>
       <c r="O20" s="183">
         <f t="shared" si="6"/>
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="Q20" s="180"/>
     </row>
@@ -4409,25 +4422,23 @@
       <c r="C21" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="151" t="s">
-        <v>133</v>
-      </c>
+      <c r="D21" s="151"/>
       <c r="E21" s="152">
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="147">
-        <v>1422621.6047557367</v>
+        <v>1411097.1317416991</v>
       </c>
       <c r="G21" s="178">
-        <v>150587.20000000001</v>
+        <v>0</v>
       </c>
       <c r="H21" s="148">
         <f t="shared" si="0"/>
-        <v>1272034.4047557367</v>
+        <v>1411097.1317416991</v>
       </c>
       <c r="I21" s="148">
         <f t="shared" si="7"/>
-        <v>47065.272975962267</v>
+        <v>52210.593874442871</v>
       </c>
       <c r="J21" s="148">
         <f t="shared" si="1"/>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="K21" s="148">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>11310.683999999999</v>
       </c>
       <c r="L21" s="148">
         <f t="shared" si="3"/>
@@ -4451,7 +4462,7 @@
       </c>
       <c r="O21" s="184">
         <f t="shared" si="6"/>
-        <v>1411097.1317416991</v>
+        <v>1562548.2616261418</v>
       </c>
       <c r="Q21" s="180"/>
     </row>
@@ -4472,11 +4483,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
       <c r="G22" s="176">
         <f>F22</f>
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -4492,7 +4503,7 @@
       </c>
       <c r="K22" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>10546.845600000001</v>
       </c>
       <c r="L22" s="68">
         <f t="shared" si="3"/>
@@ -4508,7 +4519,7 @@
       </c>
       <c r="O22" s="183">
         <f t="shared" si="6"/>
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="Q22" s="180"/>
     </row>
@@ -4529,11 +4540,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>210392.39631200003</v>
+        <v>98927.13236399999</v>
       </c>
       <c r="G23" s="176">
         <f>F23</f>
-        <v>210392.39631200003</v>
+        <v>98927.13236399999</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -4549,7 +4560,7 @@
       </c>
       <c r="K23" s="24">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>12162.6576</v>
       </c>
       <c r="L23" s="68">
         <f t="shared" si="3"/>
@@ -4565,7 +4576,7 @@
       </c>
       <c r="O23" s="183">
         <f t="shared" si="6"/>
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="Q23" s="180"/>
     </row>
@@ -4584,11 +4595,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>271884.19338999997</v>
+        <v>127840.61790999999</v>
       </c>
       <c r="G24" s="176">
         <f>F24</f>
-        <v>271884.19338999997</v>
+        <v>127840.61790999999</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -4604,7 +4615,7 @@
       </c>
       <c r="K24" s="24">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>15717.444</v>
       </c>
       <c r="L24" s="68">
         <f t="shared" si="3"/>
@@ -4620,7 +4631,7 @@
       </c>
       <c r="O24" s="183">
         <f t="shared" si="6"/>
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="Q24" s="180"/>
     </row>
@@ -4641,11 +4652,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>195654.96057999998</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="G25" s="176">
         <f>F25</f>
-        <v>195654.96057999998</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -4661,7 +4672,7 @@
       </c>
       <c r="K25" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>11310.683999999999</v>
       </c>
       <c r="L25" s="68">
         <f t="shared" si="3"/>
@@ -4677,7 +4688,7 @@
       </c>
       <c r="O25" s="183">
         <f t="shared" si="6"/>
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="Q25" s="181"/>
     </row>
@@ -4696,11 +4707,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
       <c r="G26" s="176">
         <f>F26</f>
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -4716,7 +4727,7 @@
       </c>
       <c r="K26" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>10546.845600000001</v>
       </c>
       <c r="L26" s="68">
         <f t="shared" si="3"/>
@@ -4732,7 +4743,7 @@
       </c>
       <c r="O26" s="183">
         <f t="shared" si="6"/>
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="Q26" s="180"/>
     </row>
@@ -4753,18 +4764,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="147">
-        <v>3273983.895916767</v>
+        <v>3275871.2751196874</v>
       </c>
       <c r="G27" s="177">
-        <v>210392.63</v>
+        <v>98927.14</v>
       </c>
       <c r="H27" s="170">
         <f t="shared" si="0"/>
-        <v>3063591.2659167671</v>
+        <v>3176944.1351196873</v>
       </c>
       <c r="I27" s="148">
         <f t="shared" si="7"/>
-        <v>113352.87683892039</v>
+        <v>117546.93299942845</v>
       </c>
       <c r="J27" s="148">
         <f t="shared" si="1"/>
@@ -4772,7 +4783,7 @@
       </c>
       <c r="K27" s="148">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>12162.6576</v>
       </c>
       <c r="L27" s="148">
         <f t="shared" si="3"/>
@@ -4788,7 +4799,7 @@
       </c>
       <c r="O27" s="184">
         <f t="shared" si="6"/>
-        <v>3275871.2751196874</v>
+        <v>3401206.8652831158</v>
       </c>
       <c r="P27" s="182">
         <f>M27+N27</f>
@@ -4810,16 +4821,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>2338825.9344148664</v>
+        <v>2547550.7298982162</v>
       </c>
       <c r="G28" s="176"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>2338825.9344148664</v>
+        <v>2547550.7298982162</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="7"/>
-        <v>86536.559573350067</v>
+        <v>94259.377006234019</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -4840,7 +4851,7 @@
       </c>
       <c r="O28" s="183">
         <f t="shared" si="6"/>
-        <v>2547550.7298982162</v>
+        <v>2763998.3428144502</v>
       </c>
       <c r="P28" s="7"/>
     </row>
@@ -4859,11 +4870,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>195654.98029000001</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="G29" s="176">
         <f>F29</f>
-        <v>195654.98029000001</v>
+        <v>91997.454009999987</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4879,7 +4890,7 @@
       </c>
       <c r="K29" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>11310.683999999999</v>
       </c>
       <c r="L29" s="68">
         <f t="shared" si="3"/>
@@ -4895,7 +4906,7 @@
       </c>
       <c r="O29" s="183">
         <f t="shared" si="6"/>
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="P29" s="7">
         <f>M29/2</f>
@@ -4906,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1">
@@ -4926,11 +4937,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
       <c r="G30" s="176">
         <f>F30</f>
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -4946,7 +4957,7 @@
       </c>
       <c r="K30" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>10546.845600000001</v>
       </c>
       <c r="L30" s="68">
         <f t="shared" si="3"/>
@@ -4962,7 +4973,7 @@
       </c>
       <c r="O30" s="183">
         <f t="shared" si="6"/>
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1">
@@ -4980,11 +4991,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>210392.62815600002</v>
+        <v>98927.13236399999</v>
       </c>
       <c r="G31" s="176">
         <f>F31</f>
-        <v>210392.62815600002</v>
+        <v>98927.13236399999</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -5000,7 +5011,7 @@
       </c>
       <c r="K31" s="24">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>12162.6576</v>
       </c>
       <c r="L31" s="68">
         <f t="shared" si="3"/>
@@ -5016,10 +5027,10 @@
       </c>
       <c r="O31" s="183">
         <f t="shared" si="6"/>
-        <v>98927.13236399999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.6">
+        <v>106715.79716399999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5033,27 +5044,27 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>18997348.68748033</v>
+        <v>17226863.163815022</v>
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>4691108.2961447304</v>
+        <v>1983592.6250439996</v>
       </c>
       <c r="H32" s="122">
         <f>SUM(H9:H31)</f>
-        <v>14506240.391335599</v>
+        <v>15361166.411406109</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>536730.89447941736</v>
+        <v>568363.15722202614</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>200000.00000000003</v>
+        <v>117895.87263508968</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
-        <v>99999.617999999959</v>
+        <v>278066.55600000004</v>
       </c>
       <c r="L32" s="90"/>
       <c r="M32" s="54">
@@ -5066,124 +5077,124 @@
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>17226863.163815022</v>
+        <v>18373592.511993047</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="227"/>
-      <c r="C34" s="227"/>
-      <c r="D34" s="227"/>
-      <c r="E34" s="227"/>
-      <c r="F34" s="227"/>
-      <c r="G34" s="227"/>
-      <c r="H34" s="227"/>
-      <c r="I34" s="227"/>
-      <c r="J34" s="227"/>
-      <c r="K34" s="227"/>
-      <c r="L34" s="227"/>
-      <c r="M34" s="227"/>
-      <c r="N34" s="227"/>
-      <c r="O34" s="227"/>
+      <c r="B34" s="228"/>
+      <c r="C34" s="228"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="228"/>
+      <c r="F34" s="228"/>
+      <c r="G34" s="228"/>
+      <c r="H34" s="228"/>
+      <c r="I34" s="228"/>
+      <c r="J34" s="228"/>
+      <c r="K34" s="228"/>
+      <c r="L34" s="228"/>
+      <c r="M34" s="228"/>
+      <c r="N34" s="228"/>
+      <c r="O34" s="228"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="227"/>
-      <c r="C35" s="227"/>
-      <c r="D35" s="227"/>
-      <c r="E35" s="227"/>
-      <c r="F35" s="227"/>
-      <c r="G35" s="227"/>
-      <c r="H35" s="227"/>
-      <c r="I35" s="227"/>
-      <c r="J35" s="227"/>
-      <c r="K35" s="227"/>
-      <c r="L35" s="227"/>
-      <c r="M35" s="227"/>
-      <c r="N35" s="227"/>
-      <c r="O35" s="227"/>
+      <c r="B35" s="228"/>
+      <c r="C35" s="228"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="228"/>
+      <c r="F35" s="228"/>
+      <c r="G35" s="228"/>
+      <c r="H35" s="228"/>
+      <c r="I35" s="228"/>
+      <c r="J35" s="228"/>
+      <c r="K35" s="228"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="228"/>
+      <c r="N35" s="228"/>
+      <c r="O35" s="228"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="227"/>
-      <c r="C36" s="227"/>
-      <c r="D36" s="227"/>
-      <c r="E36" s="227"/>
-      <c r="F36" s="227"/>
-      <c r="G36" s="227"/>
-      <c r="H36" s="227"/>
-      <c r="I36" s="227"/>
-      <c r="J36" s="227"/>
-      <c r="K36" s="227"/>
-      <c r="L36" s="227"/>
-      <c r="M36" s="227"/>
-      <c r="N36" s="227"/>
-      <c r="O36" s="227"/>
+      <c r="B36" s="228"/>
+      <c r="C36" s="228"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="228"/>
+      <c r="F36" s="228"/>
+      <c r="G36" s="228"/>
+      <c r="H36" s="228"/>
+      <c r="I36" s="228"/>
+      <c r="J36" s="228"/>
+      <c r="K36" s="228"/>
+      <c r="L36" s="228"/>
+      <c r="M36" s="228"/>
+      <c r="N36" s="228"/>
+      <c r="O36" s="228"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="227"/>
-      <c r="C37" s="227"/>
-      <c r="D37" s="227"/>
-      <c r="E37" s="227"/>
-      <c r="F37" s="227"/>
-      <c r="G37" s="227"/>
-      <c r="H37" s="227"/>
-      <c r="I37" s="227"/>
-      <c r="J37" s="227"/>
-      <c r="K37" s="227"/>
-      <c r="L37" s="227"/>
-      <c r="M37" s="227"/>
-      <c r="N37" s="227"/>
-      <c r="O37" s="227"/>
+      <c r="B37" s="228"/>
+      <c r="C37" s="228"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="228"/>
+      <c r="F37" s="228"/>
+      <c r="G37" s="228"/>
+      <c r="H37" s="228"/>
+      <c r="I37" s="228"/>
+      <c r="J37" s="228"/>
+      <c r="K37" s="228"/>
+      <c r="L37" s="228"/>
+      <c r="M37" s="228"/>
+      <c r="N37" s="228"/>
+      <c r="O37" s="228"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="229"/>
-      <c r="B38" s="229"/>
-      <c r="C38" s="229"/>
-      <c r="D38" s="229"/>
-      <c r="E38" s="229"/>
-      <c r="F38" s="229"/>
-      <c r="G38" s="229"/>
-      <c r="H38" s="229"/>
-      <c r="I38" s="229"/>
-      <c r="J38" s="229"/>
-      <c r="K38" s="229"/>
-      <c r="L38" s="229"/>
-      <c r="M38" s="229"/>
-      <c r="N38" s="229"/>
-      <c r="O38" s="229"/>
+      <c r="A38" s="230"/>
+      <c r="B38" s="230"/>
+      <c r="C38" s="230"/>
+      <c r="D38" s="230"/>
+      <c r="E38" s="230"/>
+      <c r="F38" s="230"/>
+      <c r="G38" s="230"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="230"/>
+      <c r="J38" s="230"/>
+      <c r="K38" s="230"/>
+      <c r="L38" s="230"/>
+      <c r="M38" s="230"/>
+      <c r="N38" s="230"/>
+      <c r="O38" s="230"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="229"/>
-      <c r="B39" s="229"/>
-      <c r="C39" s="229"/>
-      <c r="D39" s="229"/>
-      <c r="E39" s="229"/>
-      <c r="F39" s="229"/>
-      <c r="G39" s="229"/>
-      <c r="H39" s="229"/>
-      <c r="I39" s="229"/>
-      <c r="J39" s="229"/>
-      <c r="K39" s="229"/>
-      <c r="L39" s="229"/>
-      <c r="M39" s="229"/>
-      <c r="N39" s="229"/>
-      <c r="O39" s="229"/>
+      <c r="A39" s="230"/>
+      <c r="B39" s="230"/>
+      <c r="C39" s="230"/>
+      <c r="D39" s="230"/>
+      <c r="E39" s="230"/>
+      <c r="F39" s="230"/>
+      <c r="G39" s="230"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="230"/>
+      <c r="J39" s="230"/>
+      <c r="K39" s="230"/>
+      <c r="L39" s="230"/>
+      <c r="M39" s="230"/>
+      <c r="N39" s="230"/>
+      <c r="O39" s="230"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="229"/>
-      <c r="B40" s="229"/>
-      <c r="C40" s="229"/>
-      <c r="D40" s="229"/>
-      <c r="E40" s="229"/>
-      <c r="F40" s="229"/>
-      <c r="G40" s="229"/>
-      <c r="H40" s="229"/>
-      <c r="I40" s="229"/>
-      <c r="J40" s="229"/>
-      <c r="K40" s="229"/>
-      <c r="L40" s="229"/>
-      <c r="M40" s="229"/>
-      <c r="N40" s="229"/>
-      <c r="O40" s="229"/>
+      <c r="A40" s="230"/>
+      <c r="B40" s="230"/>
+      <c r="C40" s="230"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="230"/>
+      <c r="J40" s="230"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
+      <c r="M40" s="230"/>
+      <c r="N40" s="230"/>
+      <c r="O40" s="230"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5208,25 +5219,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="237" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="236"/>
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="238"/>
+      <c r="G1" s="239"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5262,13 +5273,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5629,7 +5640,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5651,7 +5662,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5673,7 +5684,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5695,7 +5706,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5721,7 +5732,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5743,7 +5754,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5765,7 +5776,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5787,7 +5798,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5809,7 +5820,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
